--- a/order_detail.xlsx
+++ b/order_detail.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>订单ID</t>
   </si>
@@ -38,19 +38,61 @@
     <t>各围栏经纬度</t>
   </si>
   <si>
-    <t>1</t>
+    <t>21358</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
-    <t>9.75</t>
-  </si>
-  <si>
-    <t>4.87</t>
-  </si>
-  <si>
-    <t>68.76</t>
+    <t>5.82</t>
+  </si>
+  <si>
+    <t>125.66</t>
+  </si>
+  <si>
+    <t>65452</t>
+  </si>
+  <si>
+    <t>6.30</t>
+  </si>
+  <si>
+    <t>150.79</t>
+  </si>
+  <si>
+    <t>87949</t>
+  </si>
+  <si>
+    <t>6.21</t>
+  </si>
+  <si>
+    <t>127.86</t>
+  </si>
+  <si>
+    <t>114403</t>
+  </si>
+  <si>
+    <t>8.71</t>
+  </si>
+  <si>
+    <t>108.62</t>
+  </si>
+  <si>
+    <t>363548</t>
+  </si>
+  <si>
+    <t>6.50</t>
+  </si>
+  <si>
+    <t>51.60</t>
+  </si>
+  <si>
+    <t>120614</t>
+  </si>
+  <si>
+    <t>5.71</t>
+  </si>
+  <si>
+    <t>108.61</t>
   </si>
 </sst>
 </file>
@@ -101,7 +143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.0" customWidth="true"/>
@@ -154,15 +196,145 @@
         <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="G2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s" s="0">
+      <c r="B3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>9</v>
       </c>
     </row>

--- a/order_detail.xlsx
+++ b/order_detail.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>订单ID</t>
   </si>
@@ -26,7 +26,7 @@
     <t>订单距离</t>
   </si>
   <si>
-    <t>配送成本</t>
+    <t>路径收益</t>
   </si>
   <si>
     <t>调度量</t>
@@ -38,7 +38,7 @@
     <t>各围栏经纬度</t>
   </si>
   <si>
-    <t>21358</t>
+    <t>21326</t>
   </si>
   <si>
     <t>136(121.204216,31.263780), 245(121.215791,31.259107), 234(121.214739,31.260665), 168(121.208425,31.260665), 169(121.208425,31.263780), 137(121.204216,31.270011)</t>
@@ -47,6 +47,9 @@
     <t>5.82</t>
   </si>
   <si>
+    <t>884.26</t>
+  </si>
+  <si>
     <t>125.66</t>
   </si>
   <si>
@@ -56,13 +59,16 @@
     <t>136:121.204216,31.263780,245:121.215791,31.259107,234:121.214739,31.260665,168:121.208425,31.260665,169:121.208425,31.263780,137:121.204216,31.270011</t>
   </si>
   <si>
-    <t>65452</t>
-  </si>
-  <si>
-    <t>197(121.210530,31.282472), 275(121.217896,31.293376), 276(121.217896,31.296491), 345(121.227366,31.288703), 344(121.227366,31.285588), 335(121.226314,31.284030)</t>
-  </si>
-  <si>
-    <t>6.30</t>
+    <t>165241</t>
+  </si>
+  <si>
+    <t>197(121.210530,31.282472), 276(121.217896,31.296491), 275(121.217896,31.293376), 345(121.227366,31.288703), 344(121.227366,31.285588), 335(121.226314,31.284030)</t>
+  </si>
+  <si>
+    <t>6.39</t>
+  </si>
+  <si>
+    <t>820.01</t>
   </si>
   <si>
     <t>150.79</t>
@@ -71,10 +77,10 @@
     <t>275:26.89,276:27.49,197:17.72,344:26.17,345:25.88,335:26.63</t>
   </si>
   <si>
-    <t>197:121.210530,31.282472,275:121.217896,31.293376,276:121.217896,31.296491,345:121.227366,31.288703,344:121.227366,31.285588,335:121.226314,31.284030</t>
-  </si>
-  <si>
-    <t>87949</t>
+    <t>197:121.210530,31.282472,276:121.217896,31.296491,275:121.217896,31.293376,345:121.227366,31.288703,344:121.227366,31.285588,335:121.226314,31.284030</t>
+  </si>
+  <si>
+    <t>91522</t>
   </si>
   <si>
     <t>120(121.201060,31.284030), 142(121.204216,31.298049), 115(121.200007,31.294934), 166(121.207373,31.287145), 165(121.207373,31.280915), 164(121.207373,31.277799)</t>
@@ -83,6 +89,9 @@
     <t>6.21</t>
   </si>
   <si>
+    <t>817.12</t>
+  </si>
+  <si>
     <t>127.86</t>
   </si>
   <si>
@@ -92,49 +101,58 @@
     <t>120:121.201060,31.284030,142:121.204216,31.298049,115:121.200007,31.294934,166:121.207373,31.287145,165:121.207373,31.280915,164:121.207373,31.277799</t>
   </si>
   <si>
-    <t>114403</t>
-  </si>
-  <si>
-    <t>356(121.229470,31.279357), 380(121.232627,31.284030), 280(121.218948,31.276241), 317(121.224209,31.265338), 246(121.215791,31.262222), 239(121.214739,31.276241)</t>
-  </si>
-  <si>
-    <t>8.71</t>
-  </si>
-  <si>
-    <t>108.62</t>
-  </si>
-  <si>
-    <t>356:12.97,246:29.86,280:14.69,380:12.95,317:27.00,239:11.16</t>
-  </si>
-  <si>
-    <t>356:121.229470,31.279357,380:121.232627,31.284030,280:121.218948,31.276241,317:121.224209,31.265338,246:121.215791,31.262222,239:121.214739,31.276241</t>
-  </si>
-  <si>
-    <t>363548</t>
-  </si>
-  <si>
-    <t>509(121.252620,31.273126), 547(121.266299,31.274684), 558(121.269456,31.276241), 531(121.257881,31.277799), 456(121.245254,31.268453), 455(121.245254,31.265338), 463(121.246306,31.263780)</t>
-  </si>
-  <si>
-    <t>6.50</t>
-  </si>
-  <si>
-    <t>51.60</t>
-  </si>
-  <si>
-    <t>547:3.80,531:3.77,455:7.89,456:7.80,509:8.11,558:3.87,463:16.37</t>
-  </si>
-  <si>
-    <t>509:121.252620,31.273126,547:121.266299,31.274684,558:121.269456,31.276241,531:121.257881,31.277799,456:121.245254,31.268453,455:121.245254,31.265338,463:121.246306,31.263780</t>
-  </si>
-  <si>
-    <t>120614</t>
-  </si>
-  <si>
-    <t>435(121.242097,31.282472), 498(121.250515,31.288703), 462(121.245254,31.290261), 461(121.245254,31.287145), 470(121.246306,31.285588), 434(121.242097,31.279357)</t>
-  </si>
-  <si>
-    <t>5.71</t>
+    <t>38717</t>
+  </si>
+  <si>
+    <t>356(121.229470,31.279357), 317(121.224209,31.265338), 246(121.215791,31.262222), 236(121.214739,31.266895), 238(121.214739,31.273126), 306(121.222105,31.287145)</t>
+  </si>
+  <si>
+    <t>6.84</t>
+  </si>
+  <si>
+    <t>707.97</t>
+  </si>
+  <si>
+    <t>125.81</t>
+  </si>
+  <si>
+    <t>306:25.72,356:12.97,246:29.86,236:15.32,317:27.00,238:14.94</t>
+  </si>
+  <si>
+    <t>356:121.229470,31.279357,317:121.224209,31.265338,246:121.215791,31.262222,236:121.214739,31.266895,238:121.214739,31.273126,306:121.222105,31.287145</t>
+  </si>
+  <si>
+    <t>373815</t>
+  </si>
+  <si>
+    <t>463(121.246306,31.263780), 455(121.245254,31.265338), 456(121.245254,31.268453), 509(121.252620,31.273126), 558(121.269456,31.276241), 561(121.270508,31.274684)</t>
+  </si>
+  <si>
+    <t>5.88</t>
+  </si>
+  <si>
+    <t>267.73</t>
+  </si>
+  <si>
+    <t>47.90</t>
+  </si>
+  <si>
+    <t>561:3.86,455:7.89,456:7.80,509:8.11,558:3.87,463:16.37</t>
+  </si>
+  <si>
+    <t>463:121.246306,31.263780,455:121.245254,31.265338,456:121.245254,31.268453,509:121.252620,31.273126,558:121.269456,31.276241,561:121.270508,31.274684</t>
+  </si>
+  <si>
+    <t>195749</t>
+  </si>
+  <si>
+    <t>470(121.246306,31.285588), 498(121.250515,31.288703), 462(121.245254,31.290261), 461(121.245254,31.287145), 435(121.242097,31.282472), 434(121.242097,31.279357)</t>
+  </si>
+  <si>
+    <t>5.54</t>
+  </si>
+  <si>
+    <t>839.88</t>
   </si>
   <si>
     <t>108.61</t>
@@ -143,7 +161,7 @@
     <t>498:16.83,434:18.28,435:18.65,470:16.46,461:19.19,462:19.19</t>
   </si>
   <si>
-    <t>435:121.242097,31.282472,498:121.250515,31.288703,462:121.245254,31.290261,461:121.245254,31.287145,470:121.246306,31.285588,434:121.242097,31.279357</t>
+    <t>470:121.246306,31.285588,498:121.250515,31.288703,462:121.245254,31.290261,461:121.245254,31.287145,435:121.242097,31.282472,434:121.242097,31.279357</t>
   </si>
 </sst>
 </file>
@@ -247,146 +265,146 @@
         <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
